--- a/filer/75206119_dancake.xlsx
+++ b/filer/75206119_dancake.xlsx
@@ -7698,7 +7698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7898,21 +7898,23 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
+          <t>fsa:DisposalsOfInvestments</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
+          <t>fsa:DisposalsOfInvestments</t>
         </is>
       </c>
       <c r="D7" s="35" t="n"/>
       <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+      <c r="H7" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7927,22 +7929,26 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfInvestments</t>
+          <t>fsa:Dividend</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfInvestments</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n"/>
+          <t>fsa:Dividend</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
+      <c r="F8" s="38" t="n">
+        <v>14873</v>
+      </c>
       <c r="G8" s="38" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>0</v>
+        <v>29822</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
@@ -7958,26 +7964,22 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>fsa:Dividend</t>
+          <t>fsa:DividendIncomeRelatedToInvestments</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>fsa:Dividend</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>0</v>
-      </c>
+          <t>fsa:DividendIncomeRelatedToInvestments</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n">
-        <v>14873</v>
-      </c>
+      <c r="F9" s="35" t="n"/>
       <c r="G9" s="35" t="n">
-        <v>0</v>
+        <v>9162</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>29822</v>
+        <v>11302</v>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
@@ -7993,17 +7995,19 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>fsa:DividendIncomeRelatedToInvestments</t>
+          <t>fsa:DividendsReceivedFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>fsa:DividendIncomeRelatedToInvestments</t>
+          <t>fsa:DividendsReceivedFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D10" s="38" t="n"/>
       <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
+      <c r="F10" s="38" t="n">
+        <v>16079</v>
+      </c>
       <c r="G10" s="38" t="n">
         <v>9162</v>
       </c>
@@ -8024,25 +8028,27 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>fsa:DividendsReceivedFromParticipatingInterests</t>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>fsa:DividendsReceivedFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="F11" s="35" t="n">
-        <v>16079</v>
+        <v>0</v>
       </c>
       <c r="G11" s="35" t="n">
-        <v>9162</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>11302</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8057,27 +8063,25 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>0</v>
-      </c>
+          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
       <c r="F12" s="38" t="n">
-        <v>0</v>
+        <v>18530</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="38" t="n"/>
+        <v>11931</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>14073</v>
+      </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8092,24 +8096,22 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+          <t>fsa:IncreaseDecreaseOfRevaluationsAndDevaluationsOfInvestmentsThroughNetExchangeDifferences</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+          <t>fsa:IncreaseDecreaseOfRevaluationsAndDevaluationsOfInvestmentsThroughNetExchangeDifferences</t>
         </is>
       </c>
       <c r="D13" s="35" t="n"/>
       <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n">
-        <v>18530</v>
-      </c>
+      <c r="F13" s="35" t="n"/>
       <c r="G13" s="35" t="n">
-        <v>11931</v>
+        <v>-893</v>
       </c>
       <c r="H13" s="35" t="n">
-        <v>14073</v>
+        <v>-1227</v>
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
@@ -8125,28 +8127,22 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:InvestmentsGross</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n">
-        <v>-22792</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>2804</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>8477</v>
-      </c>
+          <t>fsa:InvestmentsGross</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
       <c r="G14" s="38" t="n">
-        <v>-37370</v>
+        <v>8381</v>
       </c>
       <c r="H14" s="38" t="n">
-        <v>-9441</v>
+        <v>8381</v>
       </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
@@ -8162,22 +8158,24 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfRevaluationsAndDevaluationsOfInvestmentsThroughNetExchangeDifferences</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfRevaluationsAndDevaluationsOfInvestmentsThroughNetExchangeDifferences</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="D15" s="35" t="n"/>
       <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
+      <c r="F15" s="35" t="n">
+        <v>16523</v>
+      </c>
       <c r="G15" s="35" t="n">
-        <v>-893</v>
+        <v>18402</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>-1227</v>
+        <v>18213</v>
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
@@ -8193,23 +8191,23 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>fsa:InvestmentsGross</t>
+          <t>fsa:LongtermReceivablesFromAssociates</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>fsa:InvestmentsGross</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="38" t="n"/>
+          <t>fsa:LongtermReceivablesFromAssociates</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>1413</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>7168</v>
+      </c>
       <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n">
-        <v>8381</v>
-      </c>
-      <c r="H16" s="38" t="n">
-        <v>8381</v>
-      </c>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="38" t="n"/>
       <c r="I16" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8224,24 +8222,24 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:LongtermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:LongtermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D17" s="35" t="n"/>
       <c r="E17" s="35" t="n"/>
       <c r="F17" s="35" t="n">
-        <v>16523</v>
+        <v>0</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>18402</v>
+        <v>0</v>
       </c>
       <c r="H17" s="35" t="n">
-        <v>18213</v>
+        <v>0</v>
       </c>
       <c r="I17" s="36" t="inlineStr">
         <is>
@@ -8257,23 +8255,23 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermReceivablesFromAssociates</t>
+          <t>fsa:ProfitLossRelatedToInvestments</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermReceivablesFromAssociates</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>1413</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>7168</v>
-      </c>
+          <t>fsa:ProfitLossRelatedToInvestments</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
       <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
+      <c r="G18" s="38" t="n">
+        <v>11931</v>
+      </c>
+      <c r="H18" s="38" t="n">
+        <v>14073</v>
+      </c>
       <c r="I18" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8288,25 +8286,27 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermReceivablesFromParticipatingInterests</t>
+          <t>fsa:RaisingOfLongtermDebt</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
+          <t>fsa:RaisingOfLongtermDebt</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>72015</v>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>21828</v>
+      </c>
       <c r="F19" s="35" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="G19" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="H19" s="35" t="n"/>
       <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8321,23 +8321,23 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossRelatedToInvestments</t>
+          <t>fsa:ReceivedDividendsFromAssociates</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossRelatedToInvestments</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
+          <t>fsa:ReceivedDividendsFromAssociates</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>11661</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>14302</v>
+      </c>
       <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n">
-        <v>11931</v>
-      </c>
-      <c r="H20" s="38" t="n">
-        <v>14073</v>
-      </c>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
       <c r="I20" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8352,27 +8352,29 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="D21" s="35" t="n">
-        <v>72015</v>
+        <v>-22792</v>
       </c>
       <c r="E21" s="35" t="n">
-        <v>21828</v>
+        <v>-25596</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>123</v>
+        <v>-34073</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="35" t="n"/>
+        <v>3297</v>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>12738</v>
+      </c>
       <c r="I21" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8387,22 +8389,20 @@
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReceivedDividendsFromAssociates</t>
+          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReceivedDividendsFromAssociates</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n">
-        <v>11661</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>14302</v>
-      </c>
+          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n"/>
+      <c r="E22" s="38" t="n"/>
       <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n"/>
+      <c r="G22" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="39" t="inlineStr">
         <is>
@@ -8418,28 +8418,22 @@
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>-22792</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>-25596</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>-34073</v>
-      </c>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
       <c r="G23" s="35" t="n">
-        <v>3297</v>
+        <v>478</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>12738</v>
+        <v>561</v>
       </c>
       <c r="I23" s="36" t="inlineStr">
         <is>
@@ -8455,21 +8449,25 @@
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReversalsOfRevaluationOfDisposedInvestments</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D24" s="38" t="n"/>
       <c r="E24" s="38" t="n"/>
-      <c r="F24" s="38" t="n"/>
+      <c r="F24" s="38" t="n">
+        <v>4145</v>
+      </c>
       <c r="G24" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="38" t="n"/>
+        <v>4124</v>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>3464</v>
+      </c>
       <c r="I24" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8484,94 +8482,30 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>-72</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>-588</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>-217</v>
+      </c>
       <c r="G25" s="35" t="n">
-        <v>478</v>
+        <v>-1376</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>561</v>
+        <v>-484</v>
       </c>
       <c r="I25" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C26" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="38" t="n"/>
-      <c r="F26" s="38" t="n">
-        <v>4145</v>
-      </c>
-      <c r="G26" s="38" t="n">
-        <v>4124</v>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>3464</v>
-      </c>
-      <c r="I26" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>-72</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>-588</v>
-      </c>
-      <c r="F27" s="35" t="n">
-        <v>-217</v>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>-1376</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>-484</v>
-      </c>
-      <c r="I27" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/75206119_dancake.xlsx
+++ b/filer/75206119_dancake.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/75206119_dancake.xlsx
+++ b/filer/75206119_dancake.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_75206119" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_75206119" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_75206119" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_75206119" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -648,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Den uafhængige revisors erklær</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3010,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4391,19 +4392,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4509,19 +4510,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -4818,6 +4819,148 @@
       </c>
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_75206119'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_75206119'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_75206119'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_75206119'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_75206119'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_75206119'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_75206119'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_75206119'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_75206119'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_75206119'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_75206119'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_75206119'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_75206119'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_75206119'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_75206119'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B105" s="17">
+        <f>'pengestrom_raw_75206119'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C105" s="17">
+        <f>'pengestrom_raw_75206119'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D105" s="17">
+        <f>'pengestrom_raw_75206119'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E105" s="17">
+        <f>'pengestrom_raw_75206119'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F105" s="17">
+        <f>'pengestrom_raw_75206119'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B106">
+        <f>IF(ABS(('pengestrom_raw_75206119'!$B$2+'pengestrom_raw_75206119'!$B$3+'pengestrom_raw_75206119'!$B$4)-'pengestrom_raw_75206119'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_75206119'!$B$2+'pengestrom_raw_75206119'!$B$3+'pengestrom_raw_75206119'!$B$4)-'pengestrom_raw_75206119'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(ABS(('pengestrom_raw_75206119'!$C$2+'pengestrom_raw_75206119'!$C$3+'pengestrom_raw_75206119'!$C$4)-'pengestrom_raw_75206119'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_75206119'!$C$2+'pengestrom_raw_75206119'!$C$3+'pengestrom_raw_75206119'!$C$4)-'pengestrom_raw_75206119'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(ABS(('pengestrom_raw_75206119'!$D$2+'pengestrom_raw_75206119'!$D$3+'pengestrom_raw_75206119'!$D$4)-'pengestrom_raw_75206119'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_75206119'!$D$2+'pengestrom_raw_75206119'!$D$3+'pengestrom_raw_75206119'!$D$4)-'pengestrom_raw_75206119'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(ABS(('pengestrom_raw_75206119'!$E$2+'pengestrom_raw_75206119'!$E$3+'pengestrom_raw_75206119'!$E$4)-'pengestrom_raw_75206119'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_75206119'!$E$2+'pengestrom_raw_75206119'!$E$3+'pengestrom_raw_75206119'!$E$4)-'pengestrom_raw_75206119'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(ABS(('pengestrom_raw_75206119'!$F$2+'pengestrom_raw_75206119'!$F$3+'pengestrom_raw_75206119'!$F$4)-'pengestrom_raw_75206119'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_75206119'!$F$2+'pengestrom_raw_75206119'!$F$3+'pengestrom_raw_75206119'!$F$4)-'pengestrom_raw_75206119'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4850,422 +4993,422 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1094438</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1241586</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1444940</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1672268</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1837193</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>1931763</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>9172</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>7353</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>19201</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>21806</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>23598</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>25525</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>-3453</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>-4087</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>644</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>-6255</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>10551</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>-18711</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>122369</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>151952</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>160662</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>181731</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>242679</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>242760</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>302926</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>337008</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>370012</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>480473</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>492968</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>530665</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>167757</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>194828</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>198892</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>211676</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>236254</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>255196</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>47653</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>61253</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>69909</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>71449</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>72425</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>73917</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>2733</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>2267</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>1951</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>4482</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>3591</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>87516</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>80927</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>101211</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>197348</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>180698</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>196783</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>19115</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>61892</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>108429</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>98720</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>114443</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>658</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>1920</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>3937</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>5377</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>7016</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>8961</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>8569</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>4727</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>7573</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>8972</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>5190</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>4154</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>16308</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>14894</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>16</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>20394</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>92709</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>97235</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>116105</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>205684</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>196597</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>217177</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>16423</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>14451</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>20932</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>39451</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>35822</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>42428</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>76286</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>82784</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>95173</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>166233</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>160775</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>174749</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>662</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>731</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>723</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>716</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>723</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>732</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>-63471</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>79112</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>62</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>71</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>81</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>130731</v>
       </c>
     </row>
   </sheetData>
@@ -5297,1171 +5440,1163 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>487</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1023</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>744</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>457</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>694</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>980</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>13285</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>11882</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>10484</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>9109</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>7713</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>6318</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>31998</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>61919</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>47037</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>32175</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>20407</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>11298</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>108667</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>107056</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>151052</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>182252</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>185146</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>179743</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>382750</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>385469</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>380001</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>379296</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>407753</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>410495</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>11701</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>11261</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>12885</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>14823</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>17667</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>16523</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>38018</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>61336</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>18547</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>35606</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>29880</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>103133</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>541136</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>565122</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>562485</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>611977</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>640446</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>709894</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
+        <v>13310</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>504517</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>648805</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>757636</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>878156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>30490</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>30490</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>30557</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>30586</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>33610</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>13310</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>16523</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>18402</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>18213</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>19846</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>640351</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>626045</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>662554</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>679066</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>741038</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>47816</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>75600</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>74740</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>85432</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>79877</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>13670</v>
+      </c>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>25710</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>33637</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>39921</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>29370</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>46887</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>87196</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>109237</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>114661</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>114802</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>126764</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>145499</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>168240</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>176459</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>207100</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>214748</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>4634</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>6110</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>5839</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>6929</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>41870</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>113980</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>98199</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>84506</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>64962</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>1858</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>3511</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>2266</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>30060</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>33089</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>40319</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>44600</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>47935</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>231094</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>327133</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>328454</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>348865</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>340740</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
-        <v>13310</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>504517</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>648805</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>757636</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Deposita</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>30490</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>30490</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>30557</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>30586</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>11965</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>13310</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>16523</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>18402</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>18213</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>585099</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>640351</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>626045</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>662554</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>679066</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Råvarer og hjælpematerialer</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>41766</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>47816</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>75600</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>74740</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>85432</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Varer under fremstilling</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>5999</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>13670</v>
-      </c>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Færdigvarer og handelsvarer</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>21623</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>25710</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>33637</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>39921</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>29370</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>69388</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>87196</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>109237</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>114661</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>114802</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>139684</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>145499</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>168240</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>176459</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>207100</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>3230</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>4634</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>6110</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>5839</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>6929</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>51724</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>41870</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>113980</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>98199</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>84506</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>1577</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>1858</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>1565</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>3511</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>2266</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>25559</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>30060</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>33089</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>40319</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>44600</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1210</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>228547</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>231094</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>327133</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>328454</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>348865</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n">
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>33935</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>55089</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>146135</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>243607</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>323369</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>352225</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>491458</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>589250</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>707274</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>790873</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>992576</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>1117503</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>1251804</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>1386340</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>1531911</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>347519</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>406637</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>552910</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>661368</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>783889</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>3471</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>5623</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>2842</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>1803</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>602826</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>685432</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>821846</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>980889</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>1155789</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>625574</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>701855</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>887807</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>887807</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>1206543</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>13060</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>9481</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>6829</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>4420</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>4493</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>21918</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>18251</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>14848</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>9555</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>9223</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>118987</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>96996</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>39309</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>18613</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>7561</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>64389</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>33935</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>55089</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>146135</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>243607</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>362324</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>352225</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>491458</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>589250</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>707274</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>947423</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="C44" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>118987</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>97119</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>39442</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>18692</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>7641</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>6910</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>5782</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>15984</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>4375</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>4394</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>22837</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>25673</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>16087</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>22436</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>14370</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>64722</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>76007</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>99059</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>102616</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>13044</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>7450</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>15869</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>17179</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>23073</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>7754</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>10437</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>21622</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>21724</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>6601</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>36564</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>24495</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>34154</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>40177</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>74266</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>134614</v>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>129984</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>127152</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>111553</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>226097</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>300278</v>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>309707</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>332663</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>308504</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>345084</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>397397</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>349149</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>351355</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>316145</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="n">
         <v>992576</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>1117503</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>1251804</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E59" s="17" t="n">
         <v>1386340</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>347519</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>406637</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>552910</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>661368</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>-1757</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>3471</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>5623</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>2842</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>537702</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>602826</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>685432</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>821846</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>980889</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>543153</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>625574</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>701855</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>887807</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>887807</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>15215</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>13060</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>9481</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>6829</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>4420</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>24035</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>21918</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>18251</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>14848</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>9555</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>102842</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>118987</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>96996</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>39309</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>18613</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>518</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>4937</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>123</v>
-      </c>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>108297</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>118987</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>97119</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>39442</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>18692</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>11138</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>6910</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>5782</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>15984</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>4375</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>13535</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>22837</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>25673</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>16087</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>22436</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>65179</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>64722</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>91828</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>76007</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>99059</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>52085</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>13044</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>7450</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>15869</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>17179</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>6681</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>7754</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>10437</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>21622</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>21724</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="n">
-        <v>43644</v>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>36564</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>24495</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>34154</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>40177</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>74266</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>134614</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>129984</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>127152</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="n">
-        <v>271938</v>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>226097</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>300278</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>309707</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>332663</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>380235</v>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>345084</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>397397</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>349149</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>351355</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="n">
-        <v>947423</v>
-      </c>
-      <c r="C59" s="16" t="n">
-        <v>992576</v>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>1117503</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>1251804</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>1386340</v>
+      <c r="F59" s="17" t="n">
+        <v>1531911</v>
       </c>
     </row>
   </sheetData>
@@ -6470,6 +6605,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>106299</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>106623</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>211074</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>225696</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>208426</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-104177</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-44842</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-56513</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-68797</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-114900</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-32576</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-40627</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-63515</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-59427</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-13764</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6500,13 +6757,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7220,7 +7477,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7338,7 +7595,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7514,7 +7771,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7692,7 +7949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7737,27 +7994,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7784,13 +8041,13 @@
       </c>
       <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
+      <c r="F3" s="35" t="n">
+        <v>10021</v>
+      </c>
       <c r="G3" s="35" t="n">
-        <v>10021</v>
-      </c>
-      <c r="H3" s="35" t="n">
         <v>8142</v>
       </c>
+      <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7815,13 +8072,13 @@
       </c>
       <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
+      <c r="F4" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="38" t="n">
-        <v>0</v>
-      </c>
+      <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7846,13 +8103,13 @@
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+      <c r="F5" s="35" t="n">
+        <v>3</v>
+      </c>
       <c r="G5" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="35" t="n">
         <v>-1732</v>
       </c>
+      <c r="H5" s="35" t="n"/>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7877,12 +8134,14 @@
       </c>
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
+      <c r="F6" s="38" t="n">
+        <v>11931</v>
+      </c>
       <c r="G6" s="38" t="n">
-        <v>11931</v>
+        <v>14073</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>14073</v>
+        <v>15587</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7908,13 +8167,13 @@
       </c>
       <c r="D7" s="35" t="n"/>
       <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+      <c r="F7" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="H7" s="35" t="n"/>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7937,18 +8196,18 @@
           <t>fsa:Dividend</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n">
+        <v>14873</v>
+      </c>
+      <c r="F8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n">
-        <v>14873</v>
-      </c>
       <c r="G8" s="38" t="n">
+        <v>29822</v>
+      </c>
+      <c r="H8" s="38" t="n">
         <v>0</v>
-      </c>
-      <c r="H8" s="38" t="n">
-        <v>29822</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
@@ -7974,13 +8233,13 @@
       </c>
       <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
+      <c r="F9" s="35" t="n">
+        <v>9162</v>
+      </c>
       <c r="G9" s="35" t="n">
-        <v>9162</v>
-      </c>
-      <c r="H9" s="35" t="n">
         <v>11302</v>
       </c>
+      <c r="H9" s="35" t="n"/>
       <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8004,15 +8263,17 @@
         </is>
       </c>
       <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
+      <c r="E10" s="38" t="n">
+        <v>16079</v>
+      </c>
       <c r="F10" s="38" t="n">
-        <v>16079</v>
+        <v>9162</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>9162</v>
+        <v>11302</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>11302</v>
+        <v>14006</v>
       </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
@@ -8045,9 +8306,7 @@
       <c r="F11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="G11" s="35" t="n"/>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
         <is>
@@ -8072,15 +8331,17 @@
         </is>
       </c>
       <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
+      <c r="E12" s="38" t="n">
+        <v>18530</v>
+      </c>
       <c r="F12" s="38" t="n">
-        <v>18530</v>
+        <v>11931</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>11931</v>
+        <v>14073</v>
       </c>
       <c r="H12" s="38" t="n">
-        <v>14073</v>
+        <v>15587</v>
       </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
@@ -8106,13 +8367,13 @@
       </c>
       <c r="D13" s="35" t="n"/>
       <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
+      <c r="F13" s="35" t="n">
+        <v>-893</v>
+      </c>
       <c r="G13" s="35" t="n">
-        <v>-893</v>
-      </c>
-      <c r="H13" s="35" t="n">
         <v>-1227</v>
       </c>
+      <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8137,13 +8398,13 @@
       </c>
       <c r="D14" s="38" t="n"/>
       <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
+      <c r="F14" s="38" t="n">
+        <v>8381</v>
+      </c>
       <c r="G14" s="38" t="n">
         <v>8381</v>
       </c>
-      <c r="H14" s="38" t="n">
-        <v>8381</v>
-      </c>
+      <c r="H14" s="38" t="n"/>
       <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8167,15 +8428,17 @@
         </is>
       </c>
       <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
+      <c r="E15" s="35" t="n">
+        <v>16523</v>
+      </c>
       <c r="F15" s="35" t="n">
-        <v>16523</v>
+        <v>18402</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>18402</v>
+        <v>18213</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>18213</v>
+        <v>19846</v>
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
@@ -8200,11 +8463,9 @@
         </is>
       </c>
       <c r="D16" s="38" t="n">
-        <v>1413</v>
-      </c>
-      <c r="E16" s="38" t="n">
         <v>7168</v>
       </c>
+      <c r="E16" s="38" t="n"/>
       <c r="F16" s="38" t="n"/>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
@@ -8231,7 +8492,9 @@
         </is>
       </c>
       <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
+      <c r="E17" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="F17" s="35" t="n">
         <v>0</v>
       </c>
@@ -8265,13 +8528,13 @@
       </c>
       <c r="D18" s="38" t="n"/>
       <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n"/>
+      <c r="F18" s="38" t="n">
+        <v>11931</v>
+      </c>
       <c r="G18" s="38" t="n">
-        <v>11931</v>
-      </c>
-      <c r="H18" s="38" t="n">
         <v>14073</v>
       </c>
+      <c r="H18" s="38" t="n"/>
       <c r="I18" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8295,17 +8558,15 @@
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>72015</v>
+        <v>21828</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>21828</v>
+        <v>123</v>
       </c>
       <c r="F19" s="35" t="n">
-        <v>123</v>
-      </c>
-      <c r="G19" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="35" t="n"/>
       <c r="H19" s="35" t="n"/>
       <c r="I19" s="36" t="inlineStr">
         <is>
@@ -8330,11 +8591,9 @@
         </is>
       </c>
       <c r="D20" s="38" t="n">
-        <v>11661</v>
-      </c>
-      <c r="E20" s="38" t="n">
         <v>14302</v>
       </c>
+      <c r="E20" s="38" t="n"/>
       <c r="F20" s="38" t="n"/>
       <c r="G20" s="38" t="n"/>
       <c r="H20" s="38" t="n"/>
@@ -8361,19 +8620,19 @@
         </is>
       </c>
       <c r="D21" s="35" t="n">
-        <v>-22792</v>
+        <v>-25596</v>
       </c>
       <c r="E21" s="35" t="n">
-        <v>-25596</v>
+        <v>-34073</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>-34073</v>
+        <v>3297</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>3297</v>
+        <v>12738</v>
       </c>
       <c r="H21" s="35" t="n">
-        <v>12738</v>
+        <v>20218</v>
       </c>
       <c r="I21" s="36" t="inlineStr">
         <is>
@@ -8399,10 +8658,10 @@
       </c>
       <c r="D22" s="38" t="n"/>
       <c r="E22" s="38" t="n"/>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n">
+      <c r="F22" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="G22" s="38" t="n"/>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="39" t="inlineStr">
         <is>
@@ -8428,12 +8687,14 @@
       </c>
       <c r="D23" s="35" t="n"/>
       <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
+      <c r="F23" s="35" t="n">
+        <v>478</v>
+      </c>
       <c r="G23" s="35" t="n">
-        <v>478</v>
+        <v>561</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="I23" s="36" t="inlineStr">
         <is>
@@ -8458,15 +8719,17 @@
         </is>
       </c>
       <c r="D24" s="38" t="n"/>
-      <c r="E24" s="38" t="n"/>
+      <c r="E24" s="38" t="n">
+        <v>4145</v>
+      </c>
       <c r="F24" s="38" t="n">
-        <v>4145</v>
+        <v>4124</v>
       </c>
       <c r="G24" s="38" t="n">
-        <v>4124</v>
+        <v>3464</v>
       </c>
       <c r="H24" s="38" t="n">
-        <v>3464</v>
+        <v>4513</v>
       </c>
       <c r="I24" s="39" t="inlineStr">
         <is>
@@ -8491,19 +8754,19 @@
         </is>
       </c>
       <c r="D25" s="35" t="n">
-        <v>-72</v>
+        <v>-588</v>
       </c>
       <c r="E25" s="35" t="n">
-        <v>-588</v>
+        <v>-217</v>
       </c>
       <c r="F25" s="35" t="n">
-        <v>-217</v>
+        <v>-1376</v>
       </c>
       <c r="G25" s="35" t="n">
-        <v>-1376</v>
+        <v>-484</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>-484</v>
+        <v>-1827</v>
       </c>
       <c r="I25" s="36" t="inlineStr">
         <is>
